--- a/DailyReport/ConsoleGeneratedReport/report (REPLACE)/Report_Day.xlsx
+++ b/DailyReport/ConsoleGeneratedReport/report (REPLACE)/Report_Day.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-105" yWindow="-105" windowWidth="22155" windowHeight="13200" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Relatorio" sheetId="1" state="visible" r:id="rId1"/>
@@ -11,7 +11,7 @@
     <sheet name="Sheet2" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="152511" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -829,39 +829,39 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AE432"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="30.3046875" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="7.84375" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="7.15234375" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="7.3828125" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="11.53515625" bestFit="1" customWidth="1" min="6" max="6"/>
-    <col width="10.69140625" bestFit="1" customWidth="1" min="7" max="7"/>
-    <col width="7.3828125" bestFit="1" customWidth="1" min="8" max="8"/>
-    <col width="11.53515625" bestFit="1" customWidth="1" min="9" max="9"/>
-    <col width="10.3828125" bestFit="1" customWidth="1" min="10" max="10"/>
-    <col width="19.3828125" bestFit="1" customWidth="1" min="11" max="11"/>
+    <col width="30.28515625" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="7.85546875" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="7.140625" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="7.42578125" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="11.5703125" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="10.7109375" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col width="7.42578125" bestFit="1" customWidth="1" min="8" max="8"/>
+    <col width="11.5703125" bestFit="1" customWidth="1" min="9" max="9"/>
+    <col width="10.42578125" bestFit="1" customWidth="1" min="10" max="10"/>
+    <col width="19.42578125" bestFit="1" customWidth="1" min="11" max="11"/>
     <col hidden="1" width="12" customWidth="1" min="12" max="12"/>
-    <col width="12.3046875" bestFit="1" customWidth="1" min="13" max="13"/>
-    <col width="11.53515625" bestFit="1" customWidth="1" min="14" max="14"/>
-    <col width="20.3828125" bestFit="1" customWidth="1" min="15" max="15"/>
-    <col hidden="1" width="8.3046875" customWidth="1" min="16" max="16"/>
-    <col width="5.84375" bestFit="1" customWidth="1" min="17" max="17"/>
-    <col width="8.53515625" bestFit="1" customWidth="1" style="25" min="18" max="18"/>
-    <col width="7.69140625" bestFit="1" customWidth="1" style="25" min="19" max="19"/>
-    <col hidden="1" width="11.15234375" customWidth="1" style="25" min="20" max="20"/>
-    <col width="11.3828125" bestFit="1" customWidth="1" style="25" min="21" max="21"/>
-    <col width="16.15234375" bestFit="1" customWidth="1" style="25" min="22" max="22"/>
-    <col width="12.3046875" bestFit="1" customWidth="1" style="25" min="23" max="23"/>
-    <col width="10.53515625" bestFit="1" customWidth="1" style="25" min="24" max="24"/>
-    <col width="12.3046875" bestFit="1" customWidth="1" style="24" min="25" max="25"/>
-    <col width="102.84375" bestFit="1" customWidth="1" min="26" max="26"/>
-    <col width="5.3828125" bestFit="1" customWidth="1" min="27" max="27"/>
-    <col width="10.69140625" bestFit="1" customWidth="1" min="28" max="28"/>
-    <col width="9.3828125" bestFit="1" customWidth="1" min="29" max="29"/>
-    <col width="12.3046875" bestFit="1" customWidth="1" min="30" max="30"/>
-    <col width="8.3828125" bestFit="1" customWidth="1" min="31" max="31"/>
+    <col width="12.28515625" bestFit="1" customWidth="1" min="13" max="13"/>
+    <col width="11.5703125" bestFit="1" customWidth="1" min="14" max="14"/>
+    <col width="20.42578125" bestFit="1" customWidth="1" min="15" max="15"/>
+    <col hidden="1" width="8.28515625" customWidth="1" min="16" max="16"/>
+    <col width="5.85546875" bestFit="1" customWidth="1" min="17" max="17"/>
+    <col width="8.5703125" bestFit="1" customWidth="1" style="25" min="18" max="18"/>
+    <col width="7.7109375" bestFit="1" customWidth="1" style="25" min="19" max="19"/>
+    <col hidden="1" width="11.140625" customWidth="1" style="25" min="20" max="20"/>
+    <col width="11.42578125" bestFit="1" customWidth="1" style="25" min="21" max="21"/>
+    <col width="16.140625" bestFit="1" customWidth="1" style="25" min="22" max="22"/>
+    <col width="12.28515625" bestFit="1" customWidth="1" style="25" min="23" max="23"/>
+    <col width="10.5703125" bestFit="1" customWidth="1" style="25" min="24" max="24"/>
+    <col width="12.28515625" bestFit="1" customWidth="1" style="24" min="25" max="25"/>
+    <col width="102.85546875" bestFit="1" customWidth="1" min="26" max="26"/>
+    <col width="5.42578125" bestFit="1" customWidth="1" min="27" max="27"/>
+    <col width="10.7109375" bestFit="1" customWidth="1" min="28" max="28"/>
+    <col width="9.42578125" bestFit="1" customWidth="1" min="29" max="29"/>
+    <col width="12.28515625" bestFit="1" customWidth="1" min="30" max="30"/>
+    <col width="8.42578125" bestFit="1" customWidth="1" min="31" max="31"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -1360,26 +1360,10 @@
         </is>
       </c>
       <c r="V6" s="28" t="n"/>
-      <c r="W6" s="17" t="inlineStr">
-        <is>
-          <t>BRANCH</t>
-        </is>
-      </c>
-      <c r="X6" s="17" t="inlineStr">
-        <is>
-          <t>###</t>
-        </is>
-      </c>
-      <c r="Y6" s="17" t="inlineStr">
-        <is>
-          <t>NOVOBANCO</t>
-        </is>
-      </c>
-      <c r="Z6" s="44" t="inlineStr">
-        <is>
-          <t>Encravamento no módulo de notas - Verificar a máquina</t>
-        </is>
-      </c>
+      <c r="W6" s="17" t="n"/>
+      <c r="X6" s="17" t="n"/>
+      <c r="Y6" s="17" t="n"/>
+      <c r="Z6" s="44" t="n"/>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" s="45" t="inlineStr">
@@ -1672,10 +1656,26 @@
         </is>
       </c>
       <c r="V9" s="28" t="n"/>
-      <c r="W9" s="17" t="n"/>
-      <c r="X9" s="17" t="n"/>
-      <c r="Y9" s="17" t="n"/>
-      <c r="Z9" s="44" t="n"/>
+      <c r="W9" s="17" t="inlineStr">
+        <is>
+          <t>BRANCH</t>
+        </is>
+      </c>
+      <c r="X9" s="17" t="inlineStr">
+        <is>
+          <t>###</t>
+        </is>
+      </c>
+      <c r="Y9" s="17" t="inlineStr">
+        <is>
+          <t>NOVOBANCO</t>
+        </is>
+      </c>
+      <c r="Z9" s="44" t="inlineStr">
+        <is>
+          <t>Saco de moedas cheio - Esvaziar o saco</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="45" t="inlineStr">
@@ -2268,10 +2268,26 @@
         <v>44</v>
       </c>
       <c r="V16" s="27" t="n"/>
-      <c r="W16" s="17" t="n"/>
-      <c r="X16" s="17" t="n"/>
-      <c r="Y16" s="17" t="n"/>
-      <c r="Z16" s="44" t="n"/>
+      <c r="W16" s="17" t="inlineStr">
+        <is>
+          <t>BRANCH</t>
+        </is>
+      </c>
+      <c r="X16" s="17" t="inlineStr">
+        <is>
+          <t>###</t>
+        </is>
+      </c>
+      <c r="Y16" s="17" t="inlineStr">
+        <is>
+          <t>NOVOBANCO</t>
+        </is>
+      </c>
+      <c r="Z16" s="44" t="inlineStr">
+        <is>
+          <t>Saco de moedas cheio - Esvaziar o saco</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" s="7" t="n">
@@ -2426,10 +2442,26 @@
         <v>293</v>
       </c>
       <c r="V18" s="28" t="n"/>
-      <c r="W18" s="17" t="n"/>
-      <c r="X18" s="17" t="n"/>
-      <c r="Y18" s="17" t="n"/>
-      <c r="Z18" s="44" t="n"/>
+      <c r="W18" s="17" t="inlineStr">
+        <is>
+          <t>BRANCH</t>
+        </is>
+      </c>
+      <c r="X18" s="17" t="inlineStr">
+        <is>
+          <t>###</t>
+        </is>
+      </c>
+      <c r="Y18" s="17" t="inlineStr">
+        <is>
+          <t>NOVOBANCO</t>
+        </is>
+      </c>
+      <c r="Z18" s="44" t="inlineStr">
+        <is>
+          <t>Encravamento no módulo de cheques - Verificar a máquina</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" s="7" t="n">
@@ -2506,10 +2538,26 @@
         </is>
       </c>
       <c r="V19" s="28" t="n"/>
-      <c r="W19" s="17" t="n"/>
-      <c r="X19" s="17" t="n"/>
-      <c r="Y19" s="17" t="n"/>
-      <c r="Z19" s="44" t="n"/>
+      <c r="W19" s="17" t="inlineStr">
+        <is>
+          <t>BRANCH</t>
+        </is>
+      </c>
+      <c r="X19" s="17" t="inlineStr">
+        <is>
+          <t>###</t>
+        </is>
+      </c>
+      <c r="Y19" s="17" t="inlineStr">
+        <is>
+          <t>NOVOBANCO</t>
+        </is>
+      </c>
+      <c r="Z19" s="44" t="inlineStr">
+        <is>
+          <t>Saco de moedas cheio - Esvaziar o saco</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" s="7" t="n">
@@ -2586,10 +2634,26 @@
         <v>7</v>
       </c>
       <c r="V20" s="28" t="n"/>
-      <c r="W20" s="17" t="n"/>
-      <c r="X20" s="17" t="n"/>
-      <c r="Y20" s="17" t="n"/>
-      <c r="Z20" s="44" t="n"/>
+      <c r="W20" s="17" t="inlineStr">
+        <is>
+          <t>BRANCH</t>
+        </is>
+      </c>
+      <c r="X20" s="17" t="inlineStr">
+        <is>
+          <t>###</t>
+        </is>
+      </c>
+      <c r="Y20" s="17" t="inlineStr">
+        <is>
+          <t>NOVOBANCO</t>
+        </is>
+      </c>
+      <c r="Z20" s="44" t="inlineStr">
+        <is>
+          <t>Encravamento no módulo de moedas - Verificar a máquina</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" s="7" t="n">
@@ -2738,10 +2802,26 @@
         <v>1</v>
       </c>
       <c r="V22" s="28" t="n"/>
-      <c r="W22" s="17" t="n"/>
-      <c r="X22" s="17" t="n"/>
-      <c r="Y22" s="17" t="n"/>
-      <c r="Z22" s="44" t="n"/>
+      <c r="W22" s="17" t="inlineStr">
+        <is>
+          <t>BRANCH</t>
+        </is>
+      </c>
+      <c r="X22" s="17" t="inlineStr">
+        <is>
+          <t>###</t>
+        </is>
+      </c>
+      <c r="Y22" s="17" t="inlineStr">
+        <is>
+          <t>NOVOBANCO</t>
+        </is>
+      </c>
+      <c r="Z22" s="44" t="inlineStr">
+        <is>
+          <t>Encravamento no módulo de cheques - Verificar a máquina</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" s="7" t="n">
@@ -2818,26 +2898,10 @@
         <v>2</v>
       </c>
       <c r="V23" s="28" t="n"/>
-      <c r="W23" s="17" t="inlineStr">
-        <is>
-          <t>BRANCH</t>
-        </is>
-      </c>
-      <c r="X23" s="17" t="inlineStr">
-        <is>
-          <t>###</t>
-        </is>
-      </c>
-      <c r="Y23" s="17" t="inlineStr">
-        <is>
-          <t>NOVOBANCO</t>
-        </is>
-      </c>
-      <c r="Z23" s="44" t="inlineStr">
-        <is>
-          <t>Saco de moedas cheio - Esvaziar o saco</t>
-        </is>
-      </c>
+      <c r="W23" s="17" t="n"/>
+      <c r="X23" s="17" t="n"/>
+      <c r="Y23" s="17" t="n"/>
+      <c r="Z23" s="44" t="n"/>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" s="7" t="n">
@@ -2998,10 +3062,26 @@
         </is>
       </c>
       <c r="V25" s="28" t="n"/>
-      <c r="W25" s="17" t="n"/>
-      <c r="X25" s="17" t="n"/>
-      <c r="Y25" s="17" t="n"/>
-      <c r="Z25" s="44" t="n"/>
+      <c r="W25" s="17" t="inlineStr">
+        <is>
+          <t>BRANCH</t>
+        </is>
+      </c>
+      <c r="X25" s="17" t="inlineStr">
+        <is>
+          <t>###</t>
+        </is>
+      </c>
+      <c r="Y25" s="17" t="inlineStr">
+        <is>
+          <t>NOVOBANCO</t>
+        </is>
+      </c>
+      <c r="Z25" s="44" t="inlineStr">
+        <is>
+          <t>Encravamento no módulo de notas - Verificar a máquina</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" s="7" t="n">
@@ -3076,10 +3156,26 @@
         <v>429</v>
       </c>
       <c r="V26" s="28" t="n"/>
-      <c r="W26" s="17" t="n"/>
-      <c r="X26" s="17" t="n"/>
-      <c r="Y26" s="17" t="n"/>
-      <c r="Z26" s="44" t="n"/>
+      <c r="W26" s="17" t="inlineStr">
+        <is>
+          <t>BRANCH</t>
+        </is>
+      </c>
+      <c r="X26" s="17" t="inlineStr">
+        <is>
+          <t>###</t>
+        </is>
+      </c>
+      <c r="Y26" s="17" t="inlineStr">
+        <is>
+          <t>NOVOBANCO</t>
+        </is>
+      </c>
+      <c r="Z26" s="44" t="inlineStr">
+        <is>
+          <t>Cassete tripartida cheia &amp; Saco de moedas cheio - Verificar a máquina</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" s="7" t="n">
@@ -3308,10 +3404,26 @@
         <v>35</v>
       </c>
       <c r="V29" s="28" t="n"/>
-      <c r="W29" s="17" t="n"/>
-      <c r="X29" s="17" t="n"/>
-      <c r="Y29" s="17" t="n"/>
-      <c r="Z29" s="44" t="n"/>
+      <c r="W29" s="17" t="inlineStr">
+        <is>
+          <t>BRANCH</t>
+        </is>
+      </c>
+      <c r="X29" s="17" t="inlineStr">
+        <is>
+          <t>###</t>
+        </is>
+      </c>
+      <c r="Y29" s="17" t="inlineStr">
+        <is>
+          <t>NOVOBANCO</t>
+        </is>
+      </c>
+      <c r="Z29" s="44" t="inlineStr">
+        <is>
+          <t>Cassete tripartida cheia - Esvaziar a tripartida</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
@@ -3466,10 +3578,26 @@
         <v>11</v>
       </c>
       <c r="V31" s="28" t="n"/>
-      <c r="W31" s="17" t="n"/>
-      <c r="X31" s="17" t="n"/>
-      <c r="Y31" s="17" t="n"/>
-      <c r="Z31" s="44" t="n"/>
+      <c r="W31" s="17" t="inlineStr">
+        <is>
+          <t>BRANCH</t>
+        </is>
+      </c>
+      <c r="X31" s="17" t="inlineStr">
+        <is>
+          <t>###</t>
+        </is>
+      </c>
+      <c r="Y31" s="17" t="inlineStr">
+        <is>
+          <t>NOVOBANCO</t>
+        </is>
+      </c>
+      <c r="Z31" s="44" t="inlineStr">
+        <is>
+          <t>Saco de moedas cheio &amp; Encravamento no módulo de cheques - Verificar a máquina</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
@@ -5072,26 +5200,10 @@
           <t xml:space="preserve">20-EUR (QUASE) | </t>
         </is>
       </c>
-      <c r="W53" s="17" t="inlineStr">
-        <is>
-          <t>BRANCH</t>
-        </is>
-      </c>
-      <c r="X53" s="17" t="inlineStr">
-        <is>
-          <t>###</t>
-        </is>
-      </c>
-      <c r="Y53" s="17" t="inlineStr">
-        <is>
-          <t>NOVOBANCO</t>
-        </is>
-      </c>
-      <c r="Z53" s="44" t="inlineStr">
-        <is>
-          <t>Encravamento no módulo de moedas - Verificar a máquina</t>
-        </is>
-      </c>
+      <c r="W53" s="17" t="n"/>
+      <c r="X53" s="17" t="n"/>
+      <c r="Y53" s="17" t="n"/>
+      <c r="Z53" s="44" t="n"/>
     </row>
     <row r="54" ht="15" customHeight="1">
       <c r="A54" s="7" t="n">
@@ -5248,26 +5360,10 @@
         <v>122</v>
       </c>
       <c r="V55" s="28" t="n"/>
-      <c r="W55" s="17" t="inlineStr">
-        <is>
-          <t>BRANCH</t>
-        </is>
-      </c>
-      <c r="X55" s="17" t="inlineStr">
-        <is>
-          <t>###</t>
-        </is>
-      </c>
-      <c r="Y55" s="17" t="inlineStr">
-        <is>
-          <t>NOVOBANCO</t>
-        </is>
-      </c>
-      <c r="Z55" s="44" t="inlineStr">
-        <is>
-          <t>Encravamento no módulo de notas - Verificar a máquina</t>
-        </is>
-      </c>
+      <c r="W55" s="17" t="n"/>
+      <c r="X55" s="17" t="n"/>
+      <c r="Y55" s="17" t="n"/>
+      <c r="Z55" s="44" t="n"/>
     </row>
     <row r="56" ht="15" customHeight="1">
       <c r="A56" s="7" t="n">
@@ -5580,10 +5676,26 @@
         <v>659</v>
       </c>
       <c r="V59" s="28" t="n"/>
-      <c r="W59" s="17" t="n"/>
-      <c r="X59" s="17" t="n"/>
-      <c r="Y59" s="17" t="n"/>
-      <c r="Z59" s="44" t="n"/>
+      <c r="W59" s="17" t="inlineStr">
+        <is>
+          <t>BRANCH</t>
+        </is>
+      </c>
+      <c r="X59" s="17" t="inlineStr">
+        <is>
+          <t>###</t>
+        </is>
+      </c>
+      <c r="Y59" s="17" t="inlineStr">
+        <is>
+          <t>NOVOBANCO</t>
+        </is>
+      </c>
+      <c r="Z59" s="44" t="inlineStr">
+        <is>
+          <t>Erro no módulo de cheques &amp; Encravamento no módulo de cheques &amp; Saco de moedas cheio - Verificar a máquina</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="15" customHeight="1">
       <c r="A60" s="7" t="n">
@@ -5675,7 +5787,7 @@
       </c>
       <c r="Z60" s="44" t="inlineStr">
         <is>
-          <t>Erro no módulo de cheques &amp; Encravamento no módulo de cheques &amp; Saco de moedas cheio - Verificar a máquina</t>
+          <t>Saco de moedas cheio &amp; Retract - Verificar a máquina</t>
         </is>
       </c>
     </row>
@@ -6380,26 +6492,10 @@
           <t xml:space="preserve">20-EUR (QUASE) | </t>
         </is>
       </c>
-      <c r="W69" s="17" t="inlineStr">
-        <is>
-          <t>BRANCH</t>
-        </is>
-      </c>
-      <c r="X69" s="17" t="inlineStr">
-        <is>
-          <t>###</t>
-        </is>
-      </c>
-      <c r="Y69" s="17" t="inlineStr">
-        <is>
-          <t>NOVOBANCO</t>
-        </is>
-      </c>
-      <c r="Z69" s="44" t="inlineStr">
-        <is>
-          <t>Encravamento no módulo de notas - Verificar a máquina</t>
-        </is>
-      </c>
+      <c r="W69" s="17" t="n"/>
+      <c r="X69" s="17" t="n"/>
+      <c r="Y69" s="17" t="n"/>
+      <c r="Z69" s="44" t="n"/>
     </row>
     <row r="70" ht="15" customHeight="1">
       <c r="A70" s="7" t="n">
@@ -6478,10 +6574,26 @@
         <v>577</v>
       </c>
       <c r="V70" s="28" t="n"/>
-      <c r="W70" s="17" t="n"/>
-      <c r="X70" s="17" t="n"/>
-      <c r="Y70" s="17" t="n"/>
-      <c r="Z70" s="44" t="n"/>
+      <c r="W70" s="17" t="inlineStr">
+        <is>
+          <t>BRANCH</t>
+        </is>
+      </c>
+      <c r="X70" s="17" t="inlineStr">
+        <is>
+          <t>###</t>
+        </is>
+      </c>
+      <c r="Y70" s="17" t="inlineStr">
+        <is>
+          <t>NOVOBANCO</t>
+        </is>
+      </c>
+      <c r="Z70" s="44" t="inlineStr">
+        <is>
+          <t>Encravamento no módulo de cheques - Verificar a máquina</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="21" customHeight="1">
       <c r="A71" s="7" t="n">
@@ -6712,26 +6824,10 @@
         <v>26</v>
       </c>
       <c r="V73" s="28" t="n"/>
-      <c r="W73" s="17" t="inlineStr">
-        <is>
-          <t>BRANCH</t>
-        </is>
-      </c>
-      <c r="X73" s="17" t="inlineStr">
-        <is>
-          <t>###</t>
-        </is>
-      </c>
-      <c r="Y73" s="17" t="inlineStr">
-        <is>
-          <t>NOVOBANCO</t>
-        </is>
-      </c>
-      <c r="Z73" s="44" t="inlineStr">
-        <is>
-          <t>Erro no módulo de cheques - Verificar a máquina</t>
-        </is>
-      </c>
+      <c r="W73" s="17" t="n"/>
+      <c r="X73" s="17" t="n"/>
+      <c r="Y73" s="17" t="n"/>
+      <c r="Z73" s="44" t="n"/>
     </row>
     <row r="74" ht="15" customHeight="1">
       <c r="A74" s="7" t="n">
@@ -6886,10 +6982,26 @@
         <v>92</v>
       </c>
       <c r="V75" s="28" t="n"/>
-      <c r="W75" s="17" t="n"/>
-      <c r="X75" s="17" t="n"/>
-      <c r="Y75" s="17" t="n"/>
-      <c r="Z75" s="44" t="n"/>
+      <c r="W75" s="17" t="inlineStr">
+        <is>
+          <t>BRANCH</t>
+        </is>
+      </c>
+      <c r="X75" s="17" t="inlineStr">
+        <is>
+          <t>###</t>
+        </is>
+      </c>
+      <c r="Y75" s="17" t="inlineStr">
+        <is>
+          <t>NOVOBANCO</t>
+        </is>
+      </c>
+      <c r="Z75" s="44" t="inlineStr">
+        <is>
+          <t>Encravamento no módulo de notas - Verificar a máquina</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="15" customHeight="1">
       <c r="A76" s="7" t="n">
@@ -6964,10 +7076,26 @@
         <v>40</v>
       </c>
       <c r="V76" s="28" t="n"/>
-      <c r="W76" s="17" t="n"/>
-      <c r="X76" s="17" t="n"/>
-      <c r="Y76" s="17" t="n"/>
-      <c r="Z76" s="44" t="n"/>
+      <c r="W76" s="17" t="inlineStr">
+        <is>
+          <t>BRANCH</t>
+        </is>
+      </c>
+      <c r="X76" s="17" t="inlineStr">
+        <is>
+          <t>###</t>
+        </is>
+      </c>
+      <c r="Y76" s="17" t="inlineStr">
+        <is>
+          <t>NOVOBANCO</t>
+        </is>
+      </c>
+      <c r="Z76" s="44" t="inlineStr">
+        <is>
+          <t>Encravamento no módulo de moedas - Verificar a máquina</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="n">
@@ -7604,26 +7732,10 @@
         <v>52</v>
       </c>
       <c r="V85" s="28" t="n"/>
-      <c r="W85" s="17" t="inlineStr">
-        <is>
-          <t>BRANCH</t>
-        </is>
-      </c>
-      <c r="X85" s="17" t="inlineStr">
-        <is>
-          <t>###</t>
-        </is>
-      </c>
-      <c r="Y85" s="17" t="inlineStr">
-        <is>
-          <t>NOVOBANCO</t>
-        </is>
-      </c>
-      <c r="Z85" s="44" t="inlineStr">
-        <is>
-          <t>Impressora sem papel - Verificar a máquina</t>
-        </is>
-      </c>
+      <c r="W85" s="17" t="n"/>
+      <c r="X85" s="17" t="n"/>
+      <c r="Y85" s="17" t="n"/>
+      <c r="Z85" s="44" t="n"/>
     </row>
     <row r="86" ht="21" customHeight="1">
       <c r="A86" s="7" t="n">
@@ -7791,7 +7903,7 @@
       </c>
       <c r="Z87" s="44" t="inlineStr">
         <is>
-          <t>Erro no módulo de cheques - Verificar a máquina</t>
+          <t>Saco de moedas cheio - Esvaziar o saco</t>
         </is>
       </c>
     </row>
@@ -7870,10 +7982,26 @@
         <v>30</v>
       </c>
       <c r="V88" s="28" t="n"/>
-      <c r="W88" s="17" t="n"/>
-      <c r="X88" s="17" t="n"/>
-      <c r="Y88" s="17" t="n"/>
-      <c r="Z88" s="44" t="n"/>
+      <c r="W88" s="17" t="inlineStr">
+        <is>
+          <t>BRANCH</t>
+        </is>
+      </c>
+      <c r="X88" s="17" t="inlineStr">
+        <is>
+          <t>###</t>
+        </is>
+      </c>
+      <c r="Y88" s="17" t="inlineStr">
+        <is>
+          <t>NOVOBANCO</t>
+        </is>
+      </c>
+      <c r="Z88" s="44" t="inlineStr">
+        <is>
+          <t>Encravamento no módulo de cheques - Verificar a máquina</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="7" t="n">
@@ -8026,26 +8154,10 @@
         <v>79</v>
       </c>
       <c r="V90" s="28" t="n"/>
-      <c r="W90" s="17" t="inlineStr">
-        <is>
-          <t>BRANCH</t>
-        </is>
-      </c>
-      <c r="X90" s="17" t="inlineStr">
-        <is>
-          <t>###</t>
-        </is>
-      </c>
-      <c r="Y90" s="17" t="inlineStr">
-        <is>
-          <t>NOVOBANCO</t>
-        </is>
-      </c>
-      <c r="Z90" s="44" t="inlineStr">
-        <is>
-          <t>Erro no módulo de cheques &amp; Encravamento no módulo de cheques - Verificar a máquina</t>
-        </is>
-      </c>
+      <c r="W90" s="17" t="n"/>
+      <c r="X90" s="17" t="n"/>
+      <c r="Y90" s="17" t="n"/>
+      <c r="Z90" s="44" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="7" t="n">
@@ -8356,26 +8468,10 @@
         <v>266</v>
       </c>
       <c r="V94" s="28" t="n"/>
-      <c r="W94" s="17" t="inlineStr">
-        <is>
-          <t>BRANCH</t>
-        </is>
-      </c>
-      <c r="X94" s="17" t="inlineStr">
-        <is>
-          <t>###</t>
-        </is>
-      </c>
-      <c r="Y94" s="17" t="inlineStr">
-        <is>
-          <t>NOVOBANCO</t>
-        </is>
-      </c>
-      <c r="Z94" s="44" t="inlineStr">
-        <is>
-          <t>Saco de moedas cheio - Esvaziar o saco</t>
-        </is>
-      </c>
+      <c r="W94" s="17" t="n"/>
+      <c r="X94" s="17" t="n"/>
+      <c r="Y94" s="17" t="n"/>
+      <c r="Z94" s="44" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="7" t="n">
@@ -8543,7 +8639,7 @@
       </c>
       <c r="Z96" s="44" t="inlineStr">
         <is>
-          <t>Cassete tripartida cheia - Esvaziar a tripartida</t>
+          <t>Erro no módulo de cheques - Verificar a máquina</t>
         </is>
       </c>
     </row>
@@ -8620,10 +8716,26 @@
         <v>31</v>
       </c>
       <c r="V97" s="28" t="n"/>
-      <c r="W97" s="17" t="n"/>
-      <c r="X97" s="17" t="n"/>
-      <c r="Y97" s="17" t="n"/>
-      <c r="Z97" s="44" t="n"/>
+      <c r="W97" s="17" t="inlineStr">
+        <is>
+          <t>BRANCH</t>
+        </is>
+      </c>
+      <c r="X97" s="17" t="inlineStr">
+        <is>
+          <t>###</t>
+        </is>
+      </c>
+      <c r="Y97" s="17" t="inlineStr">
+        <is>
+          <t>NOVOBANCO</t>
+        </is>
+      </c>
+      <c r="Z97" s="44" t="inlineStr">
+        <is>
+          <t>Encravamento no módulo de notas - Verificar a máquina</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="15" customHeight="1">
       <c r="A98" s="7" t="n">
@@ -8698,10 +8810,26 @@
         <v>58</v>
       </c>
       <c r="V98" s="28" t="n"/>
-      <c r="W98" s="17" t="n"/>
-      <c r="X98" s="17" t="n"/>
-      <c r="Y98" s="17" t="n"/>
-      <c r="Z98" s="44" t="n"/>
+      <c r="W98" s="17" t="inlineStr">
+        <is>
+          <t>BRANCH</t>
+        </is>
+      </c>
+      <c r="X98" s="17" t="inlineStr">
+        <is>
+          <t>###</t>
+        </is>
+      </c>
+      <c r="Y98" s="17" t="inlineStr">
+        <is>
+          <t>NOVOBANCO</t>
+        </is>
+      </c>
+      <c r="Z98" s="44" t="inlineStr">
+        <is>
+          <t>Encravamento no módulo de cheques - Verificar a máquina</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="15" customHeight="1">
       <c r="A99" s="7" t="n">
@@ -8930,10 +9058,26 @@
         <v>257</v>
       </c>
       <c r="V101" s="28" t="n"/>
-      <c r="W101" s="17" t="n"/>
-      <c r="X101" s="17" t="n"/>
-      <c r="Y101" s="17" t="n"/>
-      <c r="Z101" s="44" t="n"/>
+      <c r="W101" s="17" t="inlineStr">
+        <is>
+          <t>BRANCH</t>
+        </is>
+      </c>
+      <c r="X101" s="17" t="inlineStr">
+        <is>
+          <t>###</t>
+        </is>
+      </c>
+      <c r="Y101" s="17" t="inlineStr">
+        <is>
+          <t>NOVOBANCO</t>
+        </is>
+      </c>
+      <c r="Z101" s="44" t="inlineStr">
+        <is>
+          <t>Encravamento no módulo de notas - Verificar a máquina</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="7" t="n">
@@ -9176,10 +9320,26 @@
         <v>354</v>
       </c>
       <c r="V104" s="28" t="n"/>
-      <c r="W104" s="17" t="n"/>
-      <c r="X104" s="17" t="n"/>
-      <c r="Y104" s="17" t="n"/>
-      <c r="Z104" s="44" t="n"/>
+      <c r="W104" s="17" t="inlineStr">
+        <is>
+          <t>BRANCH</t>
+        </is>
+      </c>
+      <c r="X104" s="17" t="inlineStr">
+        <is>
+          <t>###</t>
+        </is>
+      </c>
+      <c r="Y104" s="17" t="inlineStr">
+        <is>
+          <t>NOVOBANCO</t>
+        </is>
+      </c>
+      <c r="Z104" s="44" t="inlineStr">
+        <is>
+          <t>Saco de moedas cheio - Esvaziar o saco</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="7" t="n">
@@ -9404,26 +9564,10 @@
         <v>18</v>
       </c>
       <c r="V107" s="28" t="n"/>
-      <c r="W107" s="17" t="inlineStr">
-        <is>
-          <t>BRANCH</t>
-        </is>
-      </c>
-      <c r="X107" s="17" t="inlineStr">
-        <is>
-          <t>###</t>
-        </is>
-      </c>
-      <c r="Y107" s="17" t="inlineStr">
-        <is>
-          <t>NOVOBANCO</t>
-        </is>
-      </c>
-      <c r="Z107" s="44" t="inlineStr">
-        <is>
-          <t>Encravamento no módulo de cheques - Verificar a máquina</t>
-        </is>
-      </c>
+      <c r="W107" s="17" t="n"/>
+      <c r="X107" s="17" t="n"/>
+      <c r="Y107" s="17" t="n"/>
+      <c r="Z107" s="44" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="7" t="n">
@@ -9587,7 +9731,7 @@
       </c>
       <c r="Z109" s="44" t="inlineStr">
         <is>
-          <t>Porta do cofre aberta &amp; Encravamento no módulo de notas - Verificar a máquina</t>
+          <t>Encravamento no módulo de moedas - Verificar a máquina</t>
         </is>
       </c>
     </row>
@@ -9740,26 +9884,10 @@
         <v>28</v>
       </c>
       <c r="V111" s="28" t="n"/>
-      <c r="W111" s="17" t="inlineStr">
-        <is>
-          <t>BRANCH</t>
-        </is>
-      </c>
-      <c r="X111" s="17" t="inlineStr">
-        <is>
-          <t>###</t>
-        </is>
-      </c>
-      <c r="Y111" s="17" t="inlineStr">
-        <is>
-          <t>NOVOBANCO</t>
-        </is>
-      </c>
-      <c r="Z111" s="44" t="inlineStr">
-        <is>
-          <t>Erro no módulo de cheques - Verificar a máquina</t>
-        </is>
-      </c>
+      <c r="W111" s="17" t="n"/>
+      <c r="X111" s="17" t="n"/>
+      <c r="Y111" s="17" t="n"/>
+      <c r="Z111" s="44" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="7" t="n">
@@ -9986,26 +10114,10 @@
         <v>19</v>
       </c>
       <c r="V114" s="28" t="n"/>
-      <c r="W114" s="17" t="inlineStr">
-        <is>
-          <t>BRANCH</t>
-        </is>
-      </c>
-      <c r="X114" s="17" t="inlineStr">
-        <is>
-          <t>###</t>
-        </is>
-      </c>
-      <c r="Y114" s="17" t="inlineStr">
-        <is>
-          <t>NOVOBANCO</t>
-        </is>
-      </c>
-      <c r="Z114" s="44" t="inlineStr">
-        <is>
-          <t>Encravamento no módulo de notas - Verificar a máquina</t>
-        </is>
-      </c>
+      <c r="W114" s="17" t="n"/>
+      <c r="X114" s="17" t="n"/>
+      <c r="Y114" s="17" t="n"/>
+      <c r="Z114" s="44" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="7" t="n">
@@ -10082,10 +10194,26 @@
         <v>43</v>
       </c>
       <c r="V115" s="28" t="n"/>
-      <c r="W115" s="17" t="n"/>
-      <c r="X115" s="17" t="n"/>
-      <c r="Y115" s="17" t="n"/>
-      <c r="Z115" s="44" t="n"/>
+      <c r="W115" s="17" t="inlineStr">
+        <is>
+          <t>BRANCH</t>
+        </is>
+      </c>
+      <c r="X115" s="17" t="inlineStr">
+        <is>
+          <t>###</t>
+        </is>
+      </c>
+      <c r="Y115" s="17" t="inlineStr">
+        <is>
+          <t>NOVOBANCO</t>
+        </is>
+      </c>
+      <c r="Z115" s="44" t="inlineStr">
+        <is>
+          <t>Encravamento no módulo de moedas - Verificar a máquina</t>
+        </is>
+      </c>
     </row>
     <row r="116" ht="15" customHeight="1">
       <c r="A116" s="7" t="n">
@@ -10162,26 +10290,10 @@
         <v>47</v>
       </c>
       <c r="V116" s="28" t="n"/>
-      <c r="W116" s="17" t="inlineStr">
-        <is>
-          <t>BRANCH</t>
-        </is>
-      </c>
-      <c r="X116" s="17" t="inlineStr">
-        <is>
-          <t>###</t>
-        </is>
-      </c>
-      <c r="Y116" s="17" t="inlineStr">
-        <is>
-          <t>NOVOBANCO</t>
-        </is>
-      </c>
-      <c r="Z116" s="44" t="inlineStr">
-        <is>
-          <t>Cassete tripartida cheia - Esvaziar a tripartida</t>
-        </is>
-      </c>
+      <c r="W116" s="17" t="n"/>
+      <c r="X116" s="17" t="n"/>
+      <c r="Y116" s="17" t="n"/>
+      <c r="Z116" s="44" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="7" t="n">
@@ -10334,10 +10446,26 @@
         <v>50</v>
       </c>
       <c r="V118" s="28" t="n"/>
-      <c r="W118" s="17" t="n"/>
-      <c r="X118" s="17" t="n"/>
-      <c r="Y118" s="17" t="n"/>
-      <c r="Z118" s="44" t="n"/>
+      <c r="W118" s="17" t="inlineStr">
+        <is>
+          <t>BRANCH</t>
+        </is>
+      </c>
+      <c r="X118" s="17" t="inlineStr">
+        <is>
+          <t>###</t>
+        </is>
+      </c>
+      <c r="Y118" s="17" t="inlineStr">
+        <is>
+          <t>NOVOBANCO</t>
+        </is>
+      </c>
+      <c r="Z118" s="44" t="inlineStr">
+        <is>
+          <t>Saco de moedas cheio - Esvaziar o saco</t>
+        </is>
+      </c>
     </row>
     <row r="119" ht="15" customHeight="1">
       <c r="A119" s="7" t="n">
@@ -10650,10 +10778,26 @@
         <v>392</v>
       </c>
       <c r="V122" s="28" t="n"/>
-      <c r="W122" s="17" t="n"/>
-      <c r="X122" s="17" t="n"/>
-      <c r="Y122" s="17" t="n"/>
-      <c r="Z122" s="44" t="n"/>
+      <c r="W122" s="17" t="inlineStr">
+        <is>
+          <t>BRANCH</t>
+        </is>
+      </c>
+      <c r="X122" s="17" t="inlineStr">
+        <is>
+          <t>###</t>
+        </is>
+      </c>
+      <c r="Y122" s="17" t="inlineStr">
+        <is>
+          <t>NOVOBANCO</t>
+        </is>
+      </c>
+      <c r="Z122" s="44" t="inlineStr">
+        <is>
+          <t>Erro no módulo de cheques &amp; Encravamento no módulo de cheques - Verificar a máquina</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="7" t="n">
@@ -10732,10 +10876,26 @@
         <v>24</v>
       </c>
       <c r="V123" s="28" t="n"/>
-      <c r="W123" s="17" t="n"/>
-      <c r="X123" s="17" t="n"/>
-      <c r="Y123" s="17" t="n"/>
-      <c r="Z123" s="44" t="n"/>
+      <c r="W123" s="17" t="inlineStr">
+        <is>
+          <t>BRANCH</t>
+        </is>
+      </c>
+      <c r="X123" s="17" t="inlineStr">
+        <is>
+          <t>###</t>
+        </is>
+      </c>
+      <c r="Y123" s="17" t="inlineStr">
+        <is>
+          <t>NOVOBANCO</t>
+        </is>
+      </c>
+      <c r="Z123" s="44" t="inlineStr">
+        <is>
+          <t>Saco de moedas cheio - Esvaziar o saco</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="7" t="n">
@@ -10808,10 +10968,26 @@
         <v>27</v>
       </c>
       <c r="V124" s="28" t="n"/>
-      <c r="W124" s="17" t="n"/>
-      <c r="X124" s="17" t="n"/>
-      <c r="Y124" s="17" t="n"/>
-      <c r="Z124" s="44" t="n"/>
+      <c r="W124" s="17" t="inlineStr">
+        <is>
+          <t>BRANCH</t>
+        </is>
+      </c>
+      <c r="X124" s="17" t="inlineStr">
+        <is>
+          <t>###</t>
+        </is>
+      </c>
+      <c r="Y124" s="17" t="inlineStr">
+        <is>
+          <t>NOVOBANCO</t>
+        </is>
+      </c>
+      <c r="Z124" s="44" t="inlineStr">
+        <is>
+          <t>Encravamento na impressora - Verificar a máquina</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="7" t="n">
@@ -10880,10 +11056,26 @@
         <v>46</v>
       </c>
       <c r="V125" s="28" t="n"/>
-      <c r="W125" s="17" t="n"/>
-      <c r="X125" s="17" t="n"/>
-      <c r="Y125" s="17" t="n"/>
-      <c r="Z125" s="44" t="n"/>
+      <c r="W125" s="17" t="inlineStr">
+        <is>
+          <t>BRANCH</t>
+        </is>
+      </c>
+      <c r="X125" s="17" t="inlineStr">
+        <is>
+          <t>###</t>
+        </is>
+      </c>
+      <c r="Y125" s="17" t="inlineStr">
+        <is>
+          <t>NOVOBANCO</t>
+        </is>
+      </c>
+      <c r="Z125" s="44" t="inlineStr">
+        <is>
+          <t>Encravamento no módulo de notas - Verificar a máquina</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="7" t="n">
@@ -11034,26 +11226,10 @@
         <v>536</v>
       </c>
       <c r="V127" s="28" t="n"/>
-      <c r="W127" s="17" t="inlineStr">
-        <is>
-          <t>BRANCH</t>
-        </is>
-      </c>
-      <c r="X127" s="17" t="inlineStr">
-        <is>
-          <t>###</t>
-        </is>
-      </c>
-      <c r="Y127" s="17" t="inlineStr">
-        <is>
-          <t>NOVOBANCO</t>
-        </is>
-      </c>
-      <c r="Z127" s="44" t="inlineStr">
-        <is>
-          <t>Saco de moedas cheio - Esvaziar o saco</t>
-        </is>
-      </c>
+      <c r="W127" s="17" t="n"/>
+      <c r="X127" s="17" t="n"/>
+      <c r="Y127" s="17" t="n"/>
+      <c r="Z127" s="44" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="7" t="n">
@@ -11202,26 +11378,10 @@
         <v>128</v>
       </c>
       <c r="V129" s="28" t="n"/>
-      <c r="W129" s="17" t="inlineStr">
-        <is>
-          <t>BRANCH</t>
-        </is>
-      </c>
-      <c r="X129" s="17" t="inlineStr">
-        <is>
-          <t>###</t>
-        </is>
-      </c>
-      <c r="Y129" s="17" t="inlineStr">
-        <is>
-          <t>NOVOBANCO</t>
-        </is>
-      </c>
-      <c r="Z129" s="44" t="inlineStr">
-        <is>
-          <t>Encravamento no módulo de notas - Verificar a máquina</t>
-        </is>
-      </c>
+      <c r="W129" s="17" t="n"/>
+      <c r="X129" s="17" t="n"/>
+      <c r="Y129" s="17" t="n"/>
+      <c r="Z129" s="44" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="7" t="n">
@@ -11296,10 +11456,26 @@
         <v>41</v>
       </c>
       <c r="V130" s="28" t="n"/>
-      <c r="W130" s="17" t="n"/>
-      <c r="X130" s="17" t="n"/>
-      <c r="Y130" s="17" t="n"/>
-      <c r="Z130" s="44" t="n"/>
+      <c r="W130" s="17" t="inlineStr">
+        <is>
+          <t>BRANCH</t>
+        </is>
+      </c>
+      <c r="X130" s="17" t="inlineStr">
+        <is>
+          <t>###</t>
+        </is>
+      </c>
+      <c r="Y130" s="17" t="inlineStr">
+        <is>
+          <t>NOVOBANCO</t>
+        </is>
+      </c>
+      <c r="Z130" s="44" t="inlineStr">
+        <is>
+          <t>Saco de moedas cheio - Esvaziar o saco</t>
+        </is>
+      </c>
     </row>
     <row r="131" ht="21" customHeight="1">
       <c r="A131" s="7" t="n">
@@ -11448,26 +11624,10 @@
         <v>38</v>
       </c>
       <c r="V132" s="28" t="n"/>
-      <c r="W132" s="17" t="inlineStr">
-        <is>
-          <t>BRANCH</t>
-        </is>
-      </c>
-      <c r="X132" s="17" t="inlineStr">
-        <is>
-          <t>###</t>
-        </is>
-      </c>
-      <c r="Y132" s="17" t="inlineStr">
-        <is>
-          <t>NOVOBANCO</t>
-        </is>
-      </c>
-      <c r="Z132" s="44" t="inlineStr">
-        <is>
-          <t>Encravamento no módulo de moedas - Verificar a máquina</t>
-        </is>
-      </c>
+      <c r="W132" s="17" t="n"/>
+      <c r="X132" s="17" t="n"/>
+      <c r="Y132" s="17" t="n"/>
+      <c r="Z132" s="44" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="7" t="n">
@@ -11622,10 +11782,26 @@
         <v>15</v>
       </c>
       <c r="V134" s="28" t="n"/>
-      <c r="W134" s="17" t="n"/>
-      <c r="X134" s="17" t="n"/>
-      <c r="Y134" s="17" t="n"/>
-      <c r="Z134" s="44" t="n"/>
+      <c r="W134" s="17" t="inlineStr">
+        <is>
+          <t>BRANCH</t>
+        </is>
+      </c>
+      <c r="X134" s="17" t="inlineStr">
+        <is>
+          <t>###</t>
+        </is>
+      </c>
+      <c r="Y134" s="17" t="inlineStr">
+        <is>
+          <t>NOVOBANCO</t>
+        </is>
+      </c>
+      <c r="Z134" s="44" t="inlineStr">
+        <is>
+          <t>Saco de moedas cheio - Esvaziar o saco</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="7" t="n">
@@ -12090,10 +12266,26 @@
         <v>83</v>
       </c>
       <c r="V140" s="28" t="n"/>
-      <c r="W140" s="17" t="n"/>
-      <c r="X140" s="17" t="n"/>
-      <c r="Y140" s="17" t="n"/>
-      <c r="Z140" s="44" t="n"/>
+      <c r="W140" s="17" t="inlineStr">
+        <is>
+          <t>BRANCH</t>
+        </is>
+      </c>
+      <c r="X140" s="17" t="inlineStr">
+        <is>
+          <t>###</t>
+        </is>
+      </c>
+      <c r="Y140" s="17" t="inlineStr">
+        <is>
+          <t>NOVOBANCO</t>
+        </is>
+      </c>
+      <c r="Z140" s="44" t="inlineStr">
+        <is>
+          <t>Saco de moedas cheio - Esvaziar o saco</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="7" t="n">
@@ -12166,10 +12358,26 @@
         <v>52</v>
       </c>
       <c r="V141" s="28" t="n"/>
-      <c r="W141" s="17" t="n"/>
-      <c r="X141" s="17" t="n"/>
-      <c r="Y141" s="17" t="n"/>
-      <c r="Z141" s="44" t="n"/>
+      <c r="W141" s="17" t="inlineStr">
+        <is>
+          <t>BRANCH</t>
+        </is>
+      </c>
+      <c r="X141" s="17" t="inlineStr">
+        <is>
+          <t>###</t>
+        </is>
+      </c>
+      <c r="Y141" s="17" t="inlineStr">
+        <is>
+          <t>NOVOBANCO</t>
+        </is>
+      </c>
+      <c r="Z141" s="44" t="inlineStr">
+        <is>
+          <t>Encravamento na impressora &amp; Saco de moedas cheio - Verificar a máquina</t>
+        </is>
+      </c>
     </row>
     <row r="142" ht="15" customHeight="1">
       <c r="A142" s="7" t="n">
@@ -12244,10 +12452,26 @@
         <v>314</v>
       </c>
       <c r="V142" s="28" t="n"/>
-      <c r="W142" s="17" t="n"/>
-      <c r="X142" s="17" t="n"/>
-      <c r="Y142" s="17" t="n"/>
-      <c r="Z142" s="44" t="n"/>
+      <c r="W142" s="17" t="inlineStr">
+        <is>
+          <t>BRANCH</t>
+        </is>
+      </c>
+      <c r="X142" s="17" t="inlineStr">
+        <is>
+          <t>###</t>
+        </is>
+      </c>
+      <c r="Y142" s="17" t="inlineStr">
+        <is>
+          <t>NOVOBANCO</t>
+        </is>
+      </c>
+      <c r="Z142" s="44" t="inlineStr">
+        <is>
+          <t>Saco de moedas cheio - Esvaziar o saco</t>
+        </is>
+      </c>
     </row>
     <row r="143" ht="15" customHeight="1">
       <c r="A143" s="7" t="n">
@@ -12322,26 +12546,10 @@
         <v>71</v>
       </c>
       <c r="V143" s="28" t="n"/>
-      <c r="W143" s="17" t="inlineStr">
-        <is>
-          <t>BRANCH</t>
-        </is>
-      </c>
-      <c r="X143" s="17" t="inlineStr">
-        <is>
-          <t>###</t>
-        </is>
-      </c>
-      <c r="Y143" s="17" t="inlineStr">
-        <is>
-          <t>NOVOBANCO</t>
-        </is>
-      </c>
-      <c r="Z143" s="44" t="inlineStr">
-        <is>
-          <t>Encravamento no módulo de moedas - Verificar a máquina</t>
-        </is>
-      </c>
+      <c r="W143" s="17" t="n"/>
+      <c r="X143" s="17" t="n"/>
+      <c r="Y143" s="17" t="n"/>
+      <c r="Z143" s="44" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="7" t="n">
@@ -12808,10 +13016,26 @@
         <v>395</v>
       </c>
       <c r="V149" s="28" t="n"/>
-      <c r="W149" s="17" t="n"/>
-      <c r="X149" s="17" t="n"/>
-      <c r="Y149" s="17" t="n"/>
-      <c r="Z149" s="44" t="n"/>
+      <c r="W149" s="17" t="inlineStr">
+        <is>
+          <t>BRANCH</t>
+        </is>
+      </c>
+      <c r="X149" s="17" t="inlineStr">
+        <is>
+          <t>###</t>
+        </is>
+      </c>
+      <c r="Y149" s="17" t="inlineStr">
+        <is>
+          <t>NOVOBANCO</t>
+        </is>
+      </c>
+      <c r="Z149" s="44" t="inlineStr">
+        <is>
+          <t>Encravamento no módulo de notas - Verificar a máquina</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="7" t="n">
@@ -12886,10 +13110,26 @@
         <v>49</v>
       </c>
       <c r="V150" s="28" t="n"/>
-      <c r="W150" s="17" t="n"/>
-      <c r="X150" s="17" t="n"/>
-      <c r="Y150" s="17" t="n"/>
-      <c r="Z150" s="44" t="n"/>
+      <c r="W150" s="17" t="inlineStr">
+        <is>
+          <t>BRANCH</t>
+        </is>
+      </c>
+      <c r="X150" s="17" t="inlineStr">
+        <is>
+          <t>###</t>
+        </is>
+      </c>
+      <c r="Y150" s="17" t="inlineStr">
+        <is>
+          <t>NOVOBANCO</t>
+        </is>
+      </c>
+      <c r="Z150" s="44" t="inlineStr">
+        <is>
+          <t>Encravamento no módulo de notas - Verificar a máquina</t>
+        </is>
+      </c>
     </row>
     <row r="151" ht="15" customHeight="1">
       <c r="A151" s="7" t="n">
@@ -13118,26 +13358,10 @@
         <v>4</v>
       </c>
       <c r="V153" s="28" t="n"/>
-      <c r="W153" s="17" t="inlineStr">
-        <is>
-          <t>BRANCH</t>
-        </is>
-      </c>
-      <c r="X153" s="17" t="inlineStr">
-        <is>
-          <t>###</t>
-        </is>
-      </c>
-      <c r="Y153" s="17" t="inlineStr">
-        <is>
-          <t>NOVOBANCO</t>
-        </is>
-      </c>
-      <c r="Z153" s="44" t="inlineStr">
-        <is>
-          <t>Encravamento no módulo de notas - Verificar a máquina</t>
-        </is>
-      </c>
+      <c r="W153" s="17" t="n"/>
+      <c r="X153" s="17" t="n"/>
+      <c r="Y153" s="17" t="n"/>
+      <c r="Z153" s="44" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="7" t="n">
@@ -13212,26 +13436,10 @@
         <v>16</v>
       </c>
       <c r="V154" s="28" t="n"/>
-      <c r="W154" s="17" t="inlineStr">
-        <is>
-          <t>BRANCH</t>
-        </is>
-      </c>
-      <c r="X154" s="17" t="inlineStr">
-        <is>
-          <t>###</t>
-        </is>
-      </c>
-      <c r="Y154" s="17" t="inlineStr">
-        <is>
-          <t>NOVOBANCO</t>
-        </is>
-      </c>
-      <c r="Z154" s="44" t="inlineStr">
-        <is>
-          <t>Módulo de cheques desligado - Verificar a máquina</t>
-        </is>
-      </c>
+      <c r="W154" s="17" t="n"/>
+      <c r="X154" s="17" t="n"/>
+      <c r="Y154" s="17" t="n"/>
+      <c r="Z154" s="44" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="7" t="n">
@@ -13700,26 +13908,10 @@
         <v>174</v>
       </c>
       <c r="V160" s="28" t="n"/>
-      <c r="W160" s="17" t="inlineStr">
-        <is>
-          <t>BRANCH</t>
-        </is>
-      </c>
-      <c r="X160" s="17" t="inlineStr">
-        <is>
-          <t>###</t>
-        </is>
-      </c>
-      <c r="Y160" s="17" t="inlineStr">
-        <is>
-          <t>NOVOBANCO</t>
-        </is>
-      </c>
-      <c r="Z160" s="44" t="inlineStr">
-        <is>
-          <t>Porta do cofre aberta &amp; Encravamento no módulo de notas - Verificar a máquina</t>
-        </is>
-      </c>
+      <c r="W160" s="17" t="n"/>
+      <c r="X160" s="17" t="n"/>
+      <c r="Y160" s="17" t="n"/>
+      <c r="Z160" s="44" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="7" t="n">
@@ -13794,26 +13986,10 @@
         <v>116</v>
       </c>
       <c r="V161" s="28" t="n"/>
-      <c r="W161" s="17" t="inlineStr">
-        <is>
-          <t>BRANCH</t>
-        </is>
-      </c>
-      <c r="X161" s="17" t="inlineStr">
-        <is>
-          <t>###</t>
-        </is>
-      </c>
-      <c r="Y161" s="17" t="inlineStr">
-        <is>
-          <t>NOVOBANCO</t>
-        </is>
-      </c>
-      <c r="Z161" s="44" t="inlineStr">
-        <is>
-          <t>Encravamento no módulo de notas - Verificar a máquina</t>
-        </is>
-      </c>
+      <c r="W161" s="17" t="n"/>
+      <c r="X161" s="17" t="n"/>
+      <c r="Y161" s="17" t="n"/>
+      <c r="Z161" s="44" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="7" t="n">
@@ -14296,10 +14472,26 @@
         <v>38</v>
       </c>
       <c r="V167" s="28" t="n"/>
-      <c r="W167" s="17" t="n"/>
-      <c r="X167" s="17" t="n"/>
-      <c r="Y167" s="17" t="n"/>
-      <c r="Z167" s="44" t="n"/>
+      <c r="W167" s="17" t="inlineStr">
+        <is>
+          <t>BRANCH</t>
+        </is>
+      </c>
+      <c r="X167" s="17" t="inlineStr">
+        <is>
+          <t>###</t>
+        </is>
+      </c>
+      <c r="Y167" s="17" t="inlineStr">
+        <is>
+          <t>NOVOBANCO</t>
+        </is>
+      </c>
+      <c r="Z167" s="44" t="inlineStr">
+        <is>
+          <t>Saco de moedas cheio - Esvaziar o saco</t>
+        </is>
+      </c>
     </row>
     <row r="168" ht="15" customHeight="1">
       <c r="A168" s="7" t="n">
@@ -14452,10 +14644,26 @@
         <v>77</v>
       </c>
       <c r="V169" s="28" t="n"/>
-      <c r="W169" s="17" t="n"/>
-      <c r="X169" s="17" t="n"/>
-      <c r="Y169" s="17" t="n"/>
-      <c r="Z169" s="44" t="n"/>
+      <c r="W169" s="17" t="inlineStr">
+        <is>
+          <t>BRANCH</t>
+        </is>
+      </c>
+      <c r="X169" s="17" t="inlineStr">
+        <is>
+          <t>###</t>
+        </is>
+      </c>
+      <c r="Y169" s="17" t="inlineStr">
+        <is>
+          <t>NOVOBANCO</t>
+        </is>
+      </c>
+      <c r="Z169" s="44" t="inlineStr">
+        <is>
+          <t>Encravamento no módulo de notas - Verificar a máquina</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="7" t="n">
@@ -14760,26 +14968,10 @@
         <v>36</v>
       </c>
       <c r="V173" s="28" t="n"/>
-      <c r="W173" s="17" t="inlineStr">
-        <is>
-          <t>BRANCH</t>
-        </is>
-      </c>
-      <c r="X173" s="17" t="inlineStr">
-        <is>
-          <t>###</t>
-        </is>
-      </c>
-      <c r="Y173" s="17" t="inlineStr">
-        <is>
-          <t>NOVOBANCO</t>
-        </is>
-      </c>
-      <c r="Z173" s="44" t="inlineStr">
-        <is>
-          <t>Encravamento no módulo de moedas - Verificar a máquina</t>
-        </is>
-      </c>
+      <c r="W173" s="17" t="n"/>
+      <c r="X173" s="17" t="n"/>
+      <c r="Y173" s="17" t="n"/>
+      <c r="Z173" s="44" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="7" t="n">
@@ -15084,10 +15276,26 @@
         <v>487</v>
       </c>
       <c r="V177" s="28" t="n"/>
-      <c r="W177" s="17" t="n"/>
-      <c r="X177" s="17" t="n"/>
-      <c r="Y177" s="17" t="n"/>
-      <c r="Z177" s="44" t="n"/>
+      <c r="W177" s="17" t="inlineStr">
+        <is>
+          <t>BRANCH</t>
+        </is>
+      </c>
+      <c r="X177" s="17" t="inlineStr">
+        <is>
+          <t>###</t>
+        </is>
+      </c>
+      <c r="Y177" s="17" t="inlineStr">
+        <is>
+          <t>NOVOBANCO</t>
+        </is>
+      </c>
+      <c r="Z177" s="44" t="inlineStr">
+        <is>
+          <t>Erro no módulo de cheques &amp; Encravamento no módulo de cheques - Verificar a máquina</t>
+        </is>
+      </c>
     </row>
     <row r="178" ht="15" customHeight="1">
       <c r="A178" s="7" t="n">
@@ -15472,10 +15680,26 @@
         <v>95</v>
       </c>
       <c r="V182" s="28" t="n"/>
-      <c r="W182" s="17" t="n"/>
-      <c r="X182" s="17" t="n"/>
-      <c r="Y182" s="17" t="n"/>
-      <c r="Z182" s="44" t="n"/>
+      <c r="W182" s="17" t="inlineStr">
+        <is>
+          <t>BRANCH</t>
+        </is>
+      </c>
+      <c r="X182" s="17" t="inlineStr">
+        <is>
+          <t>###</t>
+        </is>
+      </c>
+      <c r="Y182" s="17" t="inlineStr">
+        <is>
+          <t>NOVOBANCO</t>
+        </is>
+      </c>
+      <c r="Z182" s="44" t="inlineStr">
+        <is>
+          <t>Saco de moedas cheio - Esvaziar o saco</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="7" t="n">
@@ -15626,26 +15850,10 @@
         <v>288</v>
       </c>
       <c r="V184" s="28" t="n"/>
-      <c r="W184" s="17" t="inlineStr">
-        <is>
-          <t>BRANCH</t>
-        </is>
-      </c>
-      <c r="X184" s="17" t="inlineStr">
-        <is>
-          <t>###</t>
-        </is>
-      </c>
-      <c r="Y184" s="17" t="inlineStr">
-        <is>
-          <t>NOVOBANCO</t>
-        </is>
-      </c>
-      <c r="Z184" s="44" t="inlineStr">
-        <is>
-          <t>Encravamento no módulo de moedas - Verificar a máquina</t>
-        </is>
-      </c>
+      <c r="W184" s="17" t="n"/>
+      <c r="X184" s="17" t="n"/>
+      <c r="Y184" s="17" t="n"/>
+      <c r="Z184" s="44" t="n"/>
     </row>
     <row r="185" ht="15" customHeight="1">
       <c r="A185" s="7" t="n">
@@ -16358,10 +16566,26 @@
         <v>134</v>
       </c>
       <c r="V193" s="28" t="n"/>
-      <c r="W193" s="17" t="n"/>
-      <c r="X193" s="17" t="n"/>
-      <c r="Y193" s="17" t="n"/>
-      <c r="Z193" s="44" t="n"/>
+      <c r="W193" s="17" t="inlineStr">
+        <is>
+          <t>BRANCH</t>
+        </is>
+      </c>
+      <c r="X193" s="17" t="inlineStr">
+        <is>
+          <t>###</t>
+        </is>
+      </c>
+      <c r="Y193" s="17" t="inlineStr">
+        <is>
+          <t>NOVOBANCO</t>
+        </is>
+      </c>
+      <c r="Z193" s="44" t="inlineStr">
+        <is>
+          <t>Erro no módulo de moedas - Verificar a máquina</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="7" t="n">
@@ -16904,10 +17128,26 @@
         <v>17</v>
       </c>
       <c r="V200" s="28" t="n"/>
-      <c r="W200" s="17" t="n"/>
-      <c r="X200" s="17" t="n"/>
-      <c r="Y200" s="17" t="n"/>
-      <c r="Z200" s="44" t="n"/>
+      <c r="W200" s="17" t="inlineStr">
+        <is>
+          <t>BRANCH</t>
+        </is>
+      </c>
+      <c r="X200" s="17" t="inlineStr">
+        <is>
+          <t>###</t>
+        </is>
+      </c>
+      <c r="Y200" s="17" t="inlineStr">
+        <is>
+          <t>NOVOBANCO</t>
+        </is>
+      </c>
+      <c r="Z200" s="44" t="inlineStr">
+        <is>
+          <t>Cassete tripartida cheia - Esvaziar a tripartida</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="7" t="n">
@@ -16978,10 +17218,26 @@
         <v>103</v>
       </c>
       <c r="V201" s="28" t="n"/>
-      <c r="W201" s="17" t="n"/>
-      <c r="X201" s="17" t="n"/>
-      <c r="Y201" s="17" t="n"/>
-      <c r="Z201" s="44" t="n"/>
+      <c r="W201" s="17" t="inlineStr">
+        <is>
+          <t>BRANCH</t>
+        </is>
+      </c>
+      <c r="X201" s="17" t="inlineStr">
+        <is>
+          <t>###</t>
+        </is>
+      </c>
+      <c r="Y201" s="17" t="inlineStr">
+        <is>
+          <t>NOVOBANCO</t>
+        </is>
+      </c>
+      <c r="Z201" s="44" t="inlineStr">
+        <is>
+          <t>Encravamento no módulo de cheques &amp; Erro no módulo de cheques - Verificar a máquina</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="7" t="n">
@@ -17132,10 +17388,26 @@
         <v>552</v>
       </c>
       <c r="V203" s="28" t="n"/>
-      <c r="W203" s="17" t="n"/>
-      <c r="X203" s="17" t="n"/>
-      <c r="Y203" s="17" t="n"/>
-      <c r="Z203" s="44" t="n"/>
+      <c r="W203" s="17" t="inlineStr">
+        <is>
+          <t>BRANCH</t>
+        </is>
+      </c>
+      <c r="X203" s="17" t="inlineStr">
+        <is>
+          <t>###</t>
+        </is>
+      </c>
+      <c r="Y203" s="17" t="inlineStr">
+        <is>
+          <t>NOVOBANCO</t>
+        </is>
+      </c>
+      <c r="Z203" s="44" t="inlineStr">
+        <is>
+          <t>Saco de moedas cheio - Esvaziar o saco</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="7" t="n">
@@ -17288,26 +17560,10 @@
         <v>493</v>
       </c>
       <c r="V205" s="28" t="n"/>
-      <c r="W205" s="17" t="inlineStr">
-        <is>
-          <t>BRANCH</t>
-        </is>
-      </c>
-      <c r="X205" s="17" t="inlineStr">
-        <is>
-          <t>###</t>
-        </is>
-      </c>
-      <c r="Y205" s="17" t="inlineStr">
-        <is>
-          <t>NOVOBANCO</t>
-        </is>
-      </c>
-      <c r="Z205" s="44" t="inlineStr">
-        <is>
-          <t>Saco de moedas cheio - Esvaziar o saco</t>
-        </is>
-      </c>
+      <c r="W205" s="17" t="n"/>
+      <c r="X205" s="17" t="n"/>
+      <c r="Y205" s="17" t="n"/>
+      <c r="Z205" s="44" t="n"/>
     </row>
     <row r="206" ht="15" customHeight="1">
       <c r="A206" s="7" t="n">
@@ -17684,10 +17940,26 @@
         <v>22</v>
       </c>
       <c r="V210" s="28" t="n"/>
-      <c r="W210" s="17" t="n"/>
-      <c r="X210" s="17" t="n"/>
-      <c r="Y210" s="17" t="n"/>
-      <c r="Z210" s="44" t="n"/>
+      <c r="W210" s="17" t="inlineStr">
+        <is>
+          <t>BRANCH</t>
+        </is>
+      </c>
+      <c r="X210" s="17" t="inlineStr">
+        <is>
+          <t>###</t>
+        </is>
+      </c>
+      <c r="Y210" s="17" t="inlineStr">
+        <is>
+          <t>NOVOBANCO</t>
+        </is>
+      </c>
+      <c r="Z210" s="44" t="inlineStr">
+        <is>
+          <t>Saco de moedas cheio - Esvaziar o saco</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="7" t="n">
@@ -17764,10 +18036,26 @@
         <v>28</v>
       </c>
       <c r="V211" s="28" t="n"/>
-      <c r="W211" s="17" t="n"/>
-      <c r="X211" s="17" t="n"/>
-      <c r="Y211" s="17" t="n"/>
-      <c r="Z211" s="44" t="n"/>
+      <c r="W211" s="17" t="inlineStr">
+        <is>
+          <t>BRANCH</t>
+        </is>
+      </c>
+      <c r="X211" s="17" t="inlineStr">
+        <is>
+          <t>###</t>
+        </is>
+      </c>
+      <c r="Y211" s="17" t="inlineStr">
+        <is>
+          <t>NOVOBANCO</t>
+        </is>
+      </c>
+      <c r="Z211" s="44" t="inlineStr">
+        <is>
+          <t>Saco de moedas cheio - Esvaziar o saco</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="7" t="n">
@@ -18318,26 +18606,10 @@
         <v>500</v>
       </c>
       <c r="V218" s="28" t="n"/>
-      <c r="W218" s="17" t="inlineStr">
-        <is>
-          <t>BRANCH</t>
-        </is>
-      </c>
-      <c r="X218" s="17" t="inlineStr">
-        <is>
-          <t>###</t>
-        </is>
-      </c>
-      <c r="Y218" s="17" t="inlineStr">
-        <is>
-          <t>NOVOBANCO</t>
-        </is>
-      </c>
-      <c r="Z218" s="44" t="inlineStr">
-        <is>
-          <t>Encravamento no módulo de notas - Verificar a máquina</t>
-        </is>
-      </c>
+      <c r="W218" s="17" t="n"/>
+      <c r="X218" s="17" t="n"/>
+      <c r="Y218" s="17" t="n"/>
+      <c r="Z218" s="44" t="n"/>
     </row>
     <row r="219" ht="15" customHeight="1">
       <c r="A219" s="7" t="n">
@@ -18806,26 +19078,10 @@
         <v>40</v>
       </c>
       <c r="V224" s="28" t="n"/>
-      <c r="W224" s="17" t="inlineStr">
-        <is>
-          <t>BRANCH</t>
-        </is>
-      </c>
-      <c r="X224" s="17" t="inlineStr">
-        <is>
-          <t>###</t>
-        </is>
-      </c>
-      <c r="Y224" s="17" t="inlineStr">
-        <is>
-          <t>NOVOBANCO</t>
-        </is>
-      </c>
-      <c r="Z224" s="44" t="inlineStr">
-        <is>
-          <t>Saco de moedas cheio - Esvaziar o saco</t>
-        </is>
-      </c>
+      <c r="W224" s="17" t="n"/>
+      <c r="X224" s="17" t="n"/>
+      <c r="Y224" s="17" t="n"/>
+      <c r="Z224" s="44" t="n"/>
     </row>
     <row r="225" ht="15" customHeight="1">
       <c r="A225" s="7" t="n">
@@ -19130,10 +19386,26 @@
         <v>15</v>
       </c>
       <c r="V228" s="28" t="n"/>
-      <c r="W228" s="17" t="n"/>
-      <c r="X228" s="17" t="n"/>
-      <c r="Y228" s="17" t="n"/>
-      <c r="Z228" s="44" t="n"/>
+      <c r="W228" s="17" t="inlineStr">
+        <is>
+          <t>BRANCH</t>
+        </is>
+      </c>
+      <c r="X228" s="17" t="inlineStr">
+        <is>
+          <t>###</t>
+        </is>
+      </c>
+      <c r="Y228" s="17" t="inlineStr">
+        <is>
+          <t>NOVOBANCO</t>
+        </is>
+      </c>
+      <c r="Z228" s="44" t="inlineStr">
+        <is>
+          <t>Saco de moedas cheio - Esvaziar o saco</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="7" t="n">
@@ -19206,26 +19478,10 @@
         <v>288</v>
       </c>
       <c r="V229" s="28" t="n"/>
-      <c r="W229" s="17" t="inlineStr">
-        <is>
-          <t>BRANCH</t>
-        </is>
-      </c>
-      <c r="X229" s="17" t="inlineStr">
-        <is>
-          <t>###</t>
-        </is>
-      </c>
-      <c r="Y229" s="17" t="inlineStr">
-        <is>
-          <t>NOVOBANCO</t>
-        </is>
-      </c>
-      <c r="Z229" s="44" t="inlineStr">
-        <is>
-          <t>Erro no módulo de cheques &amp; Encravamento no módulo de cheques - Verificar a máquina</t>
-        </is>
-      </c>
+      <c r="W229" s="17" t="n"/>
+      <c r="X229" s="17" t="n"/>
+      <c r="Y229" s="17" t="n"/>
+      <c r="Z229" s="44" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="7" t="n">
@@ -19296,10 +19552,26 @@
         <v>483</v>
       </c>
       <c r="V230" s="28" t="n"/>
-      <c r="W230" s="17" t="n"/>
-      <c r="X230" s="17" t="n"/>
-      <c r="Y230" s="17" t="n"/>
-      <c r="Z230" s="44" t="n"/>
+      <c r="W230" s="17" t="inlineStr">
+        <is>
+          <t>BRANCH</t>
+        </is>
+      </c>
+      <c r="X230" s="17" t="inlineStr">
+        <is>
+          <t>###</t>
+        </is>
+      </c>
+      <c r="Y230" s="17" t="inlineStr">
+        <is>
+          <t>NOVOBANCO</t>
+        </is>
+      </c>
+      <c r="Z230" s="44" t="inlineStr">
+        <is>
+          <t>Encravamento no módulo de notas - Verificar a máquina</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="7" t="n">
@@ -19551,7 +19823,7 @@
       </c>
       <c r="Z233" s="44" t="inlineStr">
         <is>
-          <t>Encravamento no módulo de notas - Verificar a máquina</t>
+          <t>Encravamento no módulo de cheques &amp; Encravamento no módulo de moedas &amp; Porta do cofre aberta &amp; Encravamento no módulo de notas - Verificar a máquina</t>
         </is>
       </c>
     </row>
@@ -20014,10 +20286,26 @@
         <v>81</v>
       </c>
       <c r="V239" s="28" t="n"/>
-      <c r="W239" s="17" t="n"/>
-      <c r="X239" s="17" t="n"/>
-      <c r="Y239" s="17" t="n"/>
-      <c r="Z239" s="44" t="n"/>
+      <c r="W239" s="17" t="inlineStr">
+        <is>
+          <t>BRANCH</t>
+        </is>
+      </c>
+      <c r="X239" s="17" t="inlineStr">
+        <is>
+          <t>###</t>
+        </is>
+      </c>
+      <c r="Y239" s="17" t="inlineStr">
+        <is>
+          <t>NOVOBANCO</t>
+        </is>
+      </c>
+      <c r="Z239" s="44" t="inlineStr">
+        <is>
+          <t>Encravamento no módulo de notas - Verificar a máquina</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="7" t="n">
@@ -20324,10 +20612,26 @@
         <v>67</v>
       </c>
       <c r="V243" s="28" t="n"/>
-      <c r="W243" s="17" t="n"/>
-      <c r="X243" s="17" t="n"/>
-      <c r="Y243" s="17" t="n"/>
-      <c r="Z243" s="44" t="n"/>
+      <c r="W243" s="17" t="inlineStr">
+        <is>
+          <t>BRANCH</t>
+        </is>
+      </c>
+      <c r="X243" s="17" t="inlineStr">
+        <is>
+          <t>###</t>
+        </is>
+      </c>
+      <c r="Y243" s="17" t="inlineStr">
+        <is>
+          <t>NOVOBANCO</t>
+        </is>
+      </c>
+      <c r="Z243" s="44" t="inlineStr">
+        <is>
+          <t>Encravamento no módulo de notas - Verificar a máquina</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="7" t="n">
@@ -20554,10 +20858,26 @@
         <v>394</v>
       </c>
       <c r="V246" s="28" t="n"/>
-      <c r="W246" s="17" t="n"/>
-      <c r="X246" s="17" t="n"/>
-      <c r="Y246" s="17" t="n"/>
-      <c r="Z246" s="44" t="n"/>
+      <c r="W246" s="17" t="inlineStr">
+        <is>
+          <t>BRANCH</t>
+        </is>
+      </c>
+      <c r="X246" s="17" t="inlineStr">
+        <is>
+          <t>###</t>
+        </is>
+      </c>
+      <c r="Y246" s="17" t="inlineStr">
+        <is>
+          <t>NOVOBANCO</t>
+        </is>
+      </c>
+      <c r="Z246" s="44" t="inlineStr">
+        <is>
+          <t>Cassete tripartida cheia - Esvaziar a tripartida</t>
+        </is>
+      </c>
     </row>
     <row r="247" ht="15" customHeight="1">
       <c r="A247" s="7" t="n">
@@ -20632,26 +20952,10 @@
         <v>12</v>
       </c>
       <c r="V247" s="28" t="n"/>
-      <c r="W247" s="17" t="inlineStr">
-        <is>
-          <t>BRANCH</t>
-        </is>
-      </c>
-      <c r="X247" s="17" t="inlineStr">
-        <is>
-          <t>###</t>
-        </is>
-      </c>
-      <c r="Y247" s="17" t="inlineStr">
-        <is>
-          <t>NOVOBANCO</t>
-        </is>
-      </c>
-      <c r="Z247" s="44" t="inlineStr">
-        <is>
-          <t>Encravamento no módulo de cheques - Verificar a máquina</t>
-        </is>
-      </c>
+      <c r="W247" s="17" t="n"/>
+      <c r="X247" s="17" t="n"/>
+      <c r="Y247" s="17" t="n"/>
+      <c r="Z247" s="44" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="7" t="n">
@@ -20800,10 +21104,26 @@
         <v>8</v>
       </c>
       <c r="V249" s="28" t="n"/>
-      <c r="W249" s="17" t="n"/>
-      <c r="X249" s="17" t="n"/>
-      <c r="Y249" s="17" t="n"/>
-      <c r="Z249" s="44" t="n"/>
+      <c r="W249" s="17" t="inlineStr">
+        <is>
+          <t>BRANCH</t>
+        </is>
+      </c>
+      <c r="X249" s="17" t="inlineStr">
+        <is>
+          <t>###</t>
+        </is>
+      </c>
+      <c r="Y249" s="17" t="inlineStr">
+        <is>
+          <t>NOVOBANCO</t>
+        </is>
+      </c>
+      <c r="Z249" s="44" t="inlineStr">
+        <is>
+          <t>Encravamento no módulo de moedas - Verificar a máquina</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="7" t="n">
@@ -20895,7 +21215,7 @@
       </c>
       <c r="Z250" s="44" t="inlineStr">
         <is>
-          <t>Encravamento no módulo de cheques - Verificar a máquina</t>
+          <t>Erro no módulo de cheques - Verificar a máquina</t>
         </is>
       </c>
     </row>
@@ -21054,10 +21374,26 @@
         <v>46</v>
       </c>
       <c r="V252" s="28" t="n"/>
-      <c r="W252" s="17" t="n"/>
-      <c r="X252" s="17" t="n"/>
-      <c r="Y252" s="17" t="n"/>
-      <c r="Z252" s="44" t="n"/>
+      <c r="W252" s="17" t="inlineStr">
+        <is>
+          <t>BRANCH</t>
+        </is>
+      </c>
+      <c r="X252" s="17" t="inlineStr">
+        <is>
+          <t>###</t>
+        </is>
+      </c>
+      <c r="Y252" s="17" t="inlineStr">
+        <is>
+          <t>NOVOBANCO</t>
+        </is>
+      </c>
+      <c r="Z252" s="44" t="inlineStr">
+        <is>
+          <t>Encravamento no módulo de notas - Verificar a máquina</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="7" t="n">
@@ -21288,10 +21624,26 @@
         <v>13</v>
       </c>
       <c r="V255" s="28" t="n"/>
-      <c r="W255" s="17" t="n"/>
-      <c r="X255" s="17" t="n"/>
-      <c r="Y255" s="17" t="n"/>
-      <c r="Z255" s="44" t="n"/>
+      <c r="W255" s="17" t="inlineStr">
+        <is>
+          <t>BRANCH</t>
+        </is>
+      </c>
+      <c r="X255" s="17" t="inlineStr">
+        <is>
+          <t>###</t>
+        </is>
+      </c>
+      <c r="Y255" s="17" t="inlineStr">
+        <is>
+          <t>NOVOBANCO</t>
+        </is>
+      </c>
+      <c r="Z255" s="44" t="inlineStr">
+        <is>
+          <t>Encravamento no módulo de notas - Verificar a máquina</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="7" t="n">
@@ -21368,10 +21720,26 @@
         <v>193</v>
       </c>
       <c r="V256" s="28" t="n"/>
-      <c r="W256" s="17" t="n"/>
-      <c r="X256" s="17" t="n"/>
-      <c r="Y256" s="17" t="n"/>
-      <c r="Z256" s="44" t="n"/>
+      <c r="W256" s="17" t="inlineStr">
+        <is>
+          <t>BRANCH</t>
+        </is>
+      </c>
+      <c r="X256" s="17" t="inlineStr">
+        <is>
+          <t>###</t>
+        </is>
+      </c>
+      <c r="Y256" s="17" t="inlineStr">
+        <is>
+          <t>NOVOBANCO</t>
+        </is>
+      </c>
+      <c r="Z256" s="44" t="inlineStr">
+        <is>
+          <t>Cassete tripartida cheia - Esvaziar a tripartida</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="7" t="n">
@@ -21446,26 +21814,10 @@
         <v>39</v>
       </c>
       <c r="V257" s="28" t="n"/>
-      <c r="W257" s="17" t="inlineStr">
-        <is>
-          <t>BRANCH</t>
-        </is>
-      </c>
-      <c r="X257" s="17" t="inlineStr">
-        <is>
-          <t>###</t>
-        </is>
-      </c>
-      <c r="Y257" s="17" t="inlineStr">
-        <is>
-          <t>NOVOBANCO</t>
-        </is>
-      </c>
-      <c r="Z257" s="44" t="inlineStr">
-        <is>
-          <t>Saco de moedas cheio - Esvaziar o saco</t>
-        </is>
-      </c>
+      <c r="W257" s="17" t="n"/>
+      <c r="X257" s="17" t="n"/>
+      <c r="Y257" s="17" t="n"/>
+      <c r="Z257" s="44" t="n"/>
     </row>
     <row r="258">
       <c r="A258" s="7" t="n">
@@ -21694,10 +22046,26 @@
         <v>60</v>
       </c>
       <c r="V260" s="28" t="n"/>
-      <c r="W260" s="17" t="n"/>
-      <c r="X260" s="17" t="n"/>
-      <c r="Y260" s="17" t="n"/>
-      <c r="Z260" s="44" t="n"/>
+      <c r="W260" s="17" t="inlineStr">
+        <is>
+          <t>BRANCH</t>
+        </is>
+      </c>
+      <c r="X260" s="17" t="inlineStr">
+        <is>
+          <t>###</t>
+        </is>
+      </c>
+      <c r="Y260" s="17" t="inlineStr">
+        <is>
+          <t>NOVOBANCO</t>
+        </is>
+      </c>
+      <c r="Z260" s="44" t="inlineStr">
+        <is>
+          <t>Encravamento no módulo de cheques - Verificar a máquina</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="7" t="n">
@@ -21774,10 +22142,26 @@
         <v>75</v>
       </c>
       <c r="V261" s="28" t="n"/>
-      <c r="W261" s="17" t="n"/>
-      <c r="X261" s="17" t="n"/>
-      <c r="Y261" s="17" t="n"/>
-      <c r="Z261" s="44" t="n"/>
+      <c r="W261" s="17" t="inlineStr">
+        <is>
+          <t>BRANCH</t>
+        </is>
+      </c>
+      <c r="X261" s="17" t="inlineStr">
+        <is>
+          <t>###</t>
+        </is>
+      </c>
+      <c r="Y261" s="17" t="inlineStr">
+        <is>
+          <t>NOVOBANCO</t>
+        </is>
+      </c>
+      <c r="Z261" s="44" t="inlineStr">
+        <is>
+          <t>Cassete tripartida cheia - Esvaziar a tripartida</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="7" t="n">
@@ -21848,26 +22232,10 @@
         <v>43</v>
       </c>
       <c r="V262" s="28" t="n"/>
-      <c r="W262" s="17" t="inlineStr">
-        <is>
-          <t>BRANCH</t>
-        </is>
-      </c>
-      <c r="X262" s="17" t="inlineStr">
-        <is>
-          <t>###</t>
-        </is>
-      </c>
-      <c r="Y262" s="17" t="inlineStr">
-        <is>
-          <t>NOVOBANCO</t>
-        </is>
-      </c>
-      <c r="Z262" s="44" t="inlineStr">
-        <is>
-          <t>Cassete tripartida cheia - Esvaziar a tripartida</t>
-        </is>
-      </c>
+      <c r="W262" s="17" t="n"/>
+      <c r="X262" s="17" t="n"/>
+      <c r="Y262" s="17" t="n"/>
+      <c r="Z262" s="44" t="n"/>
     </row>
     <row r="263">
       <c r="A263" s="7" t="n">
@@ -22035,7 +22403,7 @@
       </c>
       <c r="Z264" s="44" t="inlineStr">
         <is>
-          <t>Encravamento no módulo de notas - Verificar a máquina</t>
+          <t>Cassete tripartida cheia &amp; Encravamento no módulo de moedas - Verificar a máquina</t>
         </is>
       </c>
     </row>
@@ -22502,26 +22870,10 @@
         <v>24</v>
       </c>
       <c r="V270" s="28" t="n"/>
-      <c r="W270" s="17" t="inlineStr">
-        <is>
-          <t>BRANCH</t>
-        </is>
-      </c>
-      <c r="X270" s="17" t="inlineStr">
-        <is>
-          <t>###</t>
-        </is>
-      </c>
-      <c r="Y270" s="17" t="inlineStr">
-        <is>
-          <t>NOVOBANCO</t>
-        </is>
-      </c>
-      <c r="Z270" s="44" t="inlineStr">
-        <is>
-          <t>Saco de moedas cheio - Esvaziar o saco</t>
-        </is>
-      </c>
+      <c r="W270" s="17" t="n"/>
+      <c r="X270" s="17" t="n"/>
+      <c r="Y270" s="17" t="n"/>
+      <c r="Z270" s="44" t="n"/>
     </row>
     <row r="271">
       <c r="A271" s="7" t="n">
@@ -22680,10 +23032,26 @@
         <v>41</v>
       </c>
       <c r="V272" s="28" t="n"/>
-      <c r="W272" s="17" t="n"/>
-      <c r="X272" s="17" t="n"/>
-      <c r="Y272" s="17" t="n"/>
-      <c r="Z272" s="44" t="n"/>
+      <c r="W272" s="17" t="inlineStr">
+        <is>
+          <t>BRANCH</t>
+        </is>
+      </c>
+      <c r="X272" s="17" t="inlineStr">
+        <is>
+          <t>###</t>
+        </is>
+      </c>
+      <c r="Y272" s="17" t="inlineStr">
+        <is>
+          <t>NOVOBANCO</t>
+        </is>
+      </c>
+      <c r="Z272" s="44" t="inlineStr">
+        <is>
+          <t>Saco de moedas cheio - Esvaziar o saco</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="7" t="n">
@@ -22760,10 +23128,26 @@
         <v>15</v>
       </c>
       <c r="V273" s="28" t="n"/>
-      <c r="W273" s="17" t="n"/>
-      <c r="X273" s="17" t="n"/>
-      <c r="Y273" s="17" t="n"/>
-      <c r="Z273" s="44" t="n"/>
+      <c r="W273" s="17" t="inlineStr">
+        <is>
+          <t>BRANCH</t>
+        </is>
+      </c>
+      <c r="X273" s="17" t="inlineStr">
+        <is>
+          <t>###</t>
+        </is>
+      </c>
+      <c r="Y273" s="17" t="inlineStr">
+        <is>
+          <t>NOVOBANCO</t>
+        </is>
+      </c>
+      <c r="Z273" s="44" t="inlineStr">
+        <is>
+          <t>Cassete tripartida cheia - Esvaziar a tripartida</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="7" t="n">
@@ -23308,10 +23692,26 @@
         <v>20</v>
       </c>
       <c r="V280" s="28" t="n"/>
-      <c r="W280" s="17" t="n"/>
-      <c r="X280" s="17" t="n"/>
-      <c r="Y280" s="17" t="n"/>
-      <c r="Z280" s="44" t="n"/>
+      <c r="W280" s="17" t="inlineStr">
+        <is>
+          <t>BRANCH</t>
+        </is>
+      </c>
+      <c r="X280" s="17" t="inlineStr">
+        <is>
+          <t>###</t>
+        </is>
+      </c>
+      <c r="Y280" s="17" t="inlineStr">
+        <is>
+          <t>NOVOBANCO</t>
+        </is>
+      </c>
+      <c r="Z280" s="44" t="inlineStr">
+        <is>
+          <t>Encravamento no módulo de notas - Verificar a máquina</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="7" t="n">
@@ -23390,10 +23790,26 @@
         <v>21</v>
       </c>
       <c r="V281" s="28" t="n"/>
-      <c r="W281" s="17" t="n"/>
-      <c r="X281" s="17" t="n"/>
-      <c r="Y281" s="17" t="n"/>
-      <c r="Z281" s="44" t="n"/>
+      <c r="W281" s="17" t="inlineStr">
+        <is>
+          <t>BRANCH</t>
+        </is>
+      </c>
+      <c r="X281" s="17" t="inlineStr">
+        <is>
+          <t>###</t>
+        </is>
+      </c>
+      <c r="Y281" s="17" t="inlineStr">
+        <is>
+          <t>NOVOBANCO</t>
+        </is>
+      </c>
+      <c r="Z281" s="44" t="inlineStr">
+        <is>
+          <t>Saco de moedas cheio - Esvaziar o saco</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="7" t="n">
@@ -24159,8 +24575,8 @@
     <mergeCell ref="D80:D81"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="H2:J2"/>
+    <mergeCell ref="A45:N45"/>
     <mergeCell ref="D2:D3"/>
-    <mergeCell ref="A45:N45"/>
     <mergeCell ref="Q1:S1"/>
     <mergeCell ref="P2:P3"/>
     <mergeCell ref="A288:D288"/>
@@ -24172,7 +24588,6 @@
     <mergeCell ref="C80:C81"/>
     <mergeCell ref="E80:G80"/>
     <mergeCell ref="B48:B49"/>
-    <mergeCell ref="S2:S3"/>
     <mergeCell ref="D48:D49"/>
     <mergeCell ref="S13:S14"/>
     <mergeCell ref="B13:B14"/>
@@ -24192,14 +24607,15 @@
     <mergeCell ref="P13:P14"/>
     <mergeCell ref="A50:N50"/>
     <mergeCell ref="W45:Z45"/>
+    <mergeCell ref="R48:R49"/>
     <mergeCell ref="T13:T14"/>
     <mergeCell ref="Q80:Q81"/>
     <mergeCell ref="S80:S81"/>
     <mergeCell ref="Q2:Q3"/>
     <mergeCell ref="E43:G43"/>
     <mergeCell ref="R2:R3"/>
+    <mergeCell ref="E1:K1"/>
     <mergeCell ref="C48:C49"/>
-    <mergeCell ref="E1:K1"/>
     <mergeCell ref="W47:Z47"/>
     <mergeCell ref="L2:L3"/>
     <mergeCell ref="C13:C14"/>
@@ -24217,7 +24633,7 @@
     <mergeCell ref="E48:G48"/>
     <mergeCell ref="A47:D47"/>
     <mergeCell ref="A42:D42"/>
-    <mergeCell ref="R48:R49"/>
+    <mergeCell ref="S2:S3"/>
     <mergeCell ref="T48:T49"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -24232,10 +24648,10 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9.15234375" customWidth="1" style="25" min="5" max="6"/>
-    <col width="9.15234375" customWidth="1" style="24" min="7" max="7"/>
+    <col width="9.140625" customWidth="1" style="25" min="5" max="6"/>
+    <col width="9.140625" customWidth="1" style="24" min="7" max="7"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -24249,10 +24665,10 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9.15234375" customWidth="1" style="25" min="5" max="6"/>
-    <col width="9.15234375" customWidth="1" style="24" min="7" max="7"/>
+    <col width="9.140625" customWidth="1" style="25" min="5" max="6"/>
+    <col width="9.140625" customWidth="1" style="24" min="7" max="7"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/DailyReport/ConsoleGeneratedReport/report (REPLACE)/Report_Day.xlsx
+++ b/DailyReport/ConsoleGeneratedReport/report (REPLACE)/Report_Day.xlsx
@@ -2444,7 +2444,7 @@
       <c r="V18" s="28" t="n"/>
       <c r="W18" s="17" t="inlineStr">
         <is>
-          <t>BRANCH</t>
+          <t>HW ERROR</t>
         </is>
       </c>
       <c r="X18" s="17" t="inlineStr">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="Y18" s="17" t="inlineStr">
         <is>
-          <t>NOVOBANCO</t>
+          <t>PROSONIC</t>
         </is>
       </c>
       <c r="Z18" s="44" t="inlineStr">
         <is>
-          <t>Encravamento no módulo de cheques - Verificar a máquina</t>
+          <t>dfsdfsd - Enviar técnico</t>
         </is>
       </c>
     </row>
@@ -8074,10 +8074,26 @@
         <v>313</v>
       </c>
       <c r="V89" s="28" t="n"/>
-      <c r="W89" s="17" t="n"/>
-      <c r="X89" s="17" t="n"/>
-      <c r="Y89" s="17" t="n"/>
-      <c r="Z89" s="44" t="n"/>
+      <c r="W89" s="17" t="inlineStr">
+        <is>
+          <t>HW ERROR</t>
+        </is>
+      </c>
+      <c r="X89" s="17" t="inlineStr">
+        <is>
+          <t>###</t>
+        </is>
+      </c>
+      <c r="Y89" s="17" t="inlineStr">
+        <is>
+          <t>PROSONIC</t>
+        </is>
+      </c>
+      <c r="Z89" s="44" t="inlineStr">
+        <is>
+          <t>Erro no módulo de cheques - Enviar técnico</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="n">
@@ -10624,10 +10640,26 @@
         <v>354</v>
       </c>
       <c r="V120" s="28" t="n"/>
-      <c r="W120" s="17" t="n"/>
-      <c r="X120" s="17" t="n"/>
-      <c r="Y120" s="17" t="n"/>
-      <c r="Z120" s="44" t="n"/>
+      <c r="W120" s="17" t="inlineStr">
+        <is>
+          <t>HW ERROR</t>
+        </is>
+      </c>
+      <c r="X120" s="17" t="inlineStr">
+        <is>
+          <t>###</t>
+        </is>
+      </c>
+      <c r="Y120" s="17" t="inlineStr">
+        <is>
+          <t>PROSONIC</t>
+        </is>
+      </c>
+      <c r="Z120" s="44" t="inlineStr">
+        <is>
+          <t>Erro no módulo de moedas - Enviar técnico</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="7" t="n">
@@ -11952,10 +11984,26 @@
         <v>46</v>
       </c>
       <c r="V136" s="28" t="n"/>
-      <c r="W136" s="17" t="n"/>
-      <c r="X136" s="17" t="n"/>
-      <c r="Y136" s="17" t="n"/>
-      <c r="Z136" s="44" t="n"/>
+      <c r="W136" s="17" t="inlineStr">
+        <is>
+          <t>HW ERROR</t>
+        </is>
+      </c>
+      <c r="X136" s="17" t="inlineStr">
+        <is>
+          <t>###</t>
+        </is>
+      </c>
+      <c r="Y136" s="17" t="inlineStr">
+        <is>
+          <t>NOVOBANCO</t>
+        </is>
+      </c>
+      <c r="Z136" s="44" t="inlineStr">
+        <is>
+          <t>Erro no sistema de tintagem - Enviar técnico</t>
+        </is>
+      </c>
     </row>
     <row r="137" ht="15" customHeight="1">
       <c r="A137" s="7" t="n">
